--- a/analytics/exp003_content_and_conversion_tracker.xlsx
+++ b/analytics/exp003_content_and_conversion_tracker.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">

--- a/analytics/exp003_content_and_conversion_tracker.xlsx
+++ b/analytics/exp003_content_and_conversion_tracker.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn (rohitkalyan505)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">

--- a/analytics/exp003_content_and_conversion_tracker.xlsx
+++ b/analytics/exp003_content_and_conversion_tracker.xlsx
@@ -750,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="10">
         <f>IF(E4&gt;0, F4/E4, 0)</f>
